--- a/Result/profitability/3219.xlsx
+++ b/Result/profitability/3219.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.6</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1750000000000001</v>
+        <v>0.4112500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>59.83</v>
+        <v>61.37375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.51</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07500000000000012</v>
+        <v>0.3837500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>58.36</v>
+        <v>60.50375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.59</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1850000000000001</v>
+        <v>0.4625000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>58.33875</v>
+        <v>58.71625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0237500000000001</v>
+        <v>0.1850000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>52.48</v>
+        <v>53.82625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.51</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1512499999999999</v>
+        <v>0.0212500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>49.96125</v>
+        <v>51.0725</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.39</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2999999999999999</v>
+        <v>-0.0112499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>46.6875</v>
+        <v>47.05375000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.38</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3312499999999999</v>
+        <v>-0.1187499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>43.3175</v>
+        <v>44.38375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3219</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>704</v>
+      </c>
+      <c r="D75" t="n">
+        <v>194</v>
+      </c>
+      <c r="E75" t="n">
+        <v>510</v>
+      </c>
+      <c r="F75" t="n">
+        <v>72.42</v>
+      </c>
+      <c r="G75" t="n">
+        <v>220</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>31.23%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>211</v>
+      </c>
+      <c r="K75" t="n">
+        <v>157</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5225000000000002</v>
+      </c>
+      <c r="N75" t="n">
+        <v>64.465</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.541666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.530000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1335107215526687</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.449438202247191</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1746958637469587</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
